--- a/satisfaction_surveys/019_legal_service_quality_feedback--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/019_legal_service_quality_feedback--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfied',_'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfied', 'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied', 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'highly_responsive',_'label':_'highly_responsive'}</t>
+          <t>highly_responsive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Responsive', 'label': 'Highly Responsive'}</t>
+          <t>Highly Responsive</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_responsive',_'label':_'somewhat_responsive'}</t>
+          <t>somewhat_responsive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Responsive', 'label': 'Somewhat Responsive'}</t>
+          <t>Somewhat Responsive</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'not_responsive',_'label':_'not_responsive'}</t>
+          <t>not_responsive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Not Responsive', 'label': 'Not Responsive'}</t>
+          <t>Not Responsive</t>
         </is>
       </c>
     </row>
